--- a/input/old/Structure_SKN_S_SW_10_06_MD_CHNG_LOG.xlsx
+++ b/input/old/Structure_SKN_S_SW_10_06_MD_CHNG_LOG.xlsx
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Object value</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
